--- a/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_confusion_matrix.xlsx
+++ b/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_confusion_matrix.xlsx
@@ -457,10 +457,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
@@ -476,16 +476,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -495,16 +495,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
